--- a/stock_screener/output/report_20260730.xlsx
+++ b/stock_screener/output/report_20260730.xlsx
@@ -490,14 +490,14 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 箱波均戰法 — 選股結果　　2026-07-30 07:57</t>
+          <t>📊 箱波均戰法 — 選股結果　　2026-07-30 08:39</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>篩選條件：週K已買進 + 日K當日新買進訊號　|　成交量 ≥ 1000 張　|　股價 ≤ 500 元　|　掃描 670 檔 → 符合 0 檔</t>
+          <t>篩選條件：週K已買進 + 日K當日新買進訊號　|　成交量 ≥ 1000 張　|　股價 ≤ 500 元　|　掃描 489 檔 → 符合 0 檔</t>
         </is>
       </c>
     </row>
